--- a/artfynd/A 53608-2025 artfynd.xlsx
+++ b/artfynd/A 53608-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>100636385</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691870.3295191668</v>
+        <v>691870</v>
       </c>
       <c r="R2" t="n">
-        <v>6661794.235243079</v>
+        <v>6661794</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,42 +794,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109127974</v>
+        <v>110228510</v>
       </c>
       <c r="B3" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100943</v>
+        <v>100857</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Robust tickgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Dorcatoma robusta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Strand, 1938</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,26 +834,24 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fjärilsvägen, Hummelsvedjan, Upl</t>
+          <t>Grundsjömossarnas NR  i väster, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691870.3295191668</v>
+        <v>692036</v>
       </c>
       <c r="R3" t="n">
-        <v>6661794.235243079</v>
+        <v>6661991</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,22 +878,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>IBL2-fälla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,18 +901,515 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>blandskog invid häll, död stående björk</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Hans-Erik Wanntorp</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hans-Erik Wanntorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110734129</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8938</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100928</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hålskenknäppare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Eucnemis capucinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ahrens, 1812</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grundsjömossarnas NR  i väster, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>692036</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6661991</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>IBL2-fälla</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>blandskog invid häll, död stående björk</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans-Erik Wanntorp</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans-Erik Wanntorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>109127974</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen, Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>691870</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6661794</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Niclas Eklund</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Niclas Eklund, Julia Stigenberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100636370</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen, Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>691870</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6661794</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Niclas Eklund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Niclas Eklund, Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110734138</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grundsjömossarnas NR  i väster, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>692036</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6661991</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>IBL2-fälla</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>blandskog invid häll, död stående björk</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans-Erik Wanntorp</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans-Erik Wanntorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53608-2025 artfynd.xlsx
+++ b/artfynd/A 53608-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100636385</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109127974</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100636370</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110228510</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1283,6 +1308,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110734129</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1410,8 +1440,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110734138</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>